--- a/xls/kappa10cond.xlsx
+++ b/xls/kappa10cond.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2024/xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_F204AF33BA11662DCC1A6EE56B19AF2F65866912" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48436F51-B192-4F0F-9F7A-12D25B5BE82D}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_F204AF33BA11662DCC1A6EE56B19AF2F65866912" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94ACC16C-8026-4DBA-B684-1FF44AD8E454}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matriz1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
   <si>
     <t>q1</t>
   </si>
@@ -241,6 +241,15 @@
   </si>
   <si>
     <t>H1: kappa2 &gt; 0</t>
+  </si>
+  <si>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
+  </si>
+  <si>
+    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
+  </si>
+  <si>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
   </si>
 </sst>
 </file>
@@ -272,6 +281,7 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -827,10 +837,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1120,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:R41"/>
+  <dimension ref="B1:T41"/>
   <sheetFormatPr defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="2" width="2.28515625" style="5" customWidth="1"/>
@@ -1133,8 +1139,12 @@
     <col min="19" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="12" customHeight="1" thickBot="1"/>
-    <row r="2" spans="2:18" ht="10.5" customHeight="1">
+    <row r="1" spans="2:20" ht="12" customHeight="1" thickBot="1">
+      <c r="T1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="2:20" ht="10.5" customHeight="1">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="D2" s="59" t="s">
@@ -1152,8 +1162,11 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="8"/>
-    </row>
-    <row r="3" spans="2:18" ht="10.5" customHeight="1">
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" ht="10.5" customHeight="1">
       <c r="B3" s="9"/>
       <c r="D3" s="60" t="s">
         <v>23</v>
@@ -1168,12 +1181,15 @@
       <c r="L3" s="60"/>
       <c r="M3" s="60"/>
       <c r="P3" s="10"/>
-    </row>
-    <row r="4" spans="2:18" ht="10.5" customHeight="1">
+      <c r="T3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" ht="10.5" customHeight="1">
       <c r="B4" s="9"/>
       <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="2:18" ht="10.5" customHeight="1">
+    <row r="5" spans="2:20" ht="10.5" customHeight="1">
       <c r="B5" s="9"/>
       <c r="D5" s="61" t="s">
         <v>24</v>
@@ -1189,7 +1205,7 @@
       <c r="M5" s="61"/>
       <c r="P5" s="10"/>
     </row>
-    <row r="6" spans="2:18" ht="10.5" customHeight="1" thickBot="1">
+    <row r="6" spans="2:20" ht="10.5" customHeight="1" thickBot="1">
       <c r="B6" s="9"/>
       <c r="D6" s="41" t="s">
         <v>9</v>
@@ -1229,7 +1245,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="10.5" customHeight="1">
+    <row r="7" spans="2:20" ht="10.5" customHeight="1">
       <c r="B7" s="62" t="s">
         <v>25</v>
       </c>
@@ -1267,7 +1283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="10.5" customHeight="1">
+    <row r="8" spans="2:20" ht="10.5" customHeight="1">
       <c r="B8" s="62"/>
       <c r="C8" s="41" t="str">
         <f>E6</f>
@@ -1303,7 +1319,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="10.5" customHeight="1">
+    <row r="9" spans="2:20" ht="10.5" customHeight="1">
       <c r="B9" s="62"/>
       <c r="C9" s="41" t="str">
         <f>F6</f>
@@ -1339,7 +1355,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="10.5" customHeight="1">
+    <row r="10" spans="2:20" ht="10.5" customHeight="1">
       <c r="B10" s="62"/>
       <c r="C10" s="41" t="str">
         <f>G6</f>
@@ -1375,7 +1391,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:18" ht="10.5" customHeight="1">
+    <row r="11" spans="2:20" ht="10.5" customHeight="1">
       <c r="B11" s="62"/>
       <c r="C11" s="41" t="str">
         <f>H6</f>
@@ -1411,7 +1427,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="2:18" ht="10.5" customHeight="1">
+    <row r="12" spans="2:20" ht="10.5" customHeight="1">
       <c r="B12" s="62"/>
       <c r="C12" s="41" t="str">
         <f>I6</f>
@@ -1437,7 +1453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="10.5" customHeight="1">
+    <row r="13" spans="2:20" ht="10.5" customHeight="1">
       <c r="B13" s="62"/>
       <c r="C13" s="41" t="str">
         <f>J6</f>
@@ -1463,7 +1479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="10.5" customHeight="1">
+    <row r="14" spans="2:20" ht="10.5" customHeight="1">
       <c r="B14" s="62"/>
       <c r="C14" s="41" t="str">
         <f>K6</f>
@@ -1489,7 +1505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="10.5" customHeight="1">
+    <row r="15" spans="2:20" ht="10.5" customHeight="1">
       <c r="B15" s="62"/>
       <c r="C15" s="41" t="str">
         <f>L6</f>
@@ -1515,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="10.5" customHeight="1" thickBot="1">
+    <row r="16" spans="2:20" ht="10.5" customHeight="1" thickBot="1">
       <c r="B16" s="62"/>
       <c r="C16" s="41" t="str">
         <f>M6</f>

--- a/xls/kappa10cond.xlsx
+++ b/xls/kappa10cond.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_F204AF33BA11662DCC1A6EE56B19AF2F65866912" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94ACC16C-8026-4DBA-B684-1FF44AD8E454}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_F204AF33BA11662DCC1A6EE56B19AF2F65866912" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C75CAE12-BCCB-4540-9F75-A69662AA9475}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matriz1" sheetId="1" r:id="rId1"/>
@@ -837,6 +837,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1127,16 +1131,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:T41"/>
-  <sheetFormatPr defaultRowHeight="11.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="10"/>
   <cols>
-    <col min="1" max="2" width="2.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="5" customWidth="1"/>
-    <col min="4" max="13" width="8.140625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="2.140625" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="5" customWidth="1"/>
-    <col min="16" max="17" width="2.42578125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="5" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="2" width="2.26953125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" style="5" customWidth="1"/>
+    <col min="4" max="13" width="8.1796875" style="5" customWidth="1"/>
+    <col min="14" max="14" width="2.1796875" style="5" customWidth="1"/>
+    <col min="15" max="15" width="9.453125" style="5" customWidth="1"/>
+    <col min="16" max="17" width="2.453125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.1796875" style="5" hidden="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:20" ht="12" customHeight="1" thickBot="1">
@@ -1616,11 +1620,11 @@
       <c r="B19" s="9"/>
       <c r="P19" s="10"/>
     </row>
-    <row r="20" spans="2:16" ht="10.5" hidden="1" customHeight="1">
+    <row r="20" spans="2:16" ht="10.5" customHeight="1">
       <c r="B20" s="9"/>
       <c r="P20" s="10"/>
     </row>
-    <row r="21" spans="2:16" ht="10.5" hidden="1" customHeight="1">
+    <row r="21" spans="2:16" ht="10.5" customHeight="1">
       <c r="B21" s="9"/>
       <c r="D21" s="1" t="s">
         <v>0</v>
@@ -1645,7 +1649,7 @@
       </c>
       <c r="P21" s="10"/>
     </row>
-    <row r="22" spans="2:16" ht="10.5" hidden="1" customHeight="1">
+    <row r="22" spans="2:16" ht="10.5" customHeight="1">
       <c r="B22" s="9"/>
       <c r="D22" s="25">
         <f>SUM(_nii1)/O18</f>
@@ -1677,7 +1681,7 @@
       </c>
       <c r="P22" s="10"/>
     </row>
-    <row r="23" spans="2:16" ht="10.5" hidden="1" customHeight="1">
+    <row r="23" spans="2:16" ht="10.5" customHeight="1">
       <c r="B23" s="9"/>
       <c r="P23" s="10"/>
     </row>
@@ -1908,16 +1912,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:R41"/>
-  <sheetFormatPr defaultRowHeight="11.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="10"/>
   <cols>
-    <col min="1" max="2" width="2.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="5" customWidth="1"/>
-    <col min="4" max="13" width="8.140625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="2.140625" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="5" customWidth="1"/>
-    <col min="16" max="17" width="2.42578125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="5" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="2" width="2.26953125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" style="5" customWidth="1"/>
+    <col min="4" max="13" width="8.1796875" style="5" customWidth="1"/>
+    <col min="14" max="14" width="2.1796875" style="5" customWidth="1"/>
+    <col min="15" max="15" width="9.453125" style="5" customWidth="1"/>
+    <col min="16" max="17" width="2.453125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.1796875" style="5" hidden="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="12" customHeight="1" thickBot="1"/>
@@ -2678,9 +2682,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">

--- a/xls/kappa10cond.xlsx
+++ b/xls/kappa10cond.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2026/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_F204AF33BA11662DCC1A6EE56B19AF2F65866912" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C75CAE12-BCCB-4540-9F75-A69662AA9475}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="11_F204AF33BA11662DCC1A6EE56B19AF2F65866912" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCFA6344-8CEF-415C-A292-ABC7C7A7CC40}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matriz1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="46">
   <si>
     <t>q1</t>
   </si>
@@ -243,13 +243,10 @@
     <t>H1: kappa2 &gt; 0</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
-  </si>
-  <si>
-    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
-  </si>
-  <si>
     <t>#https://cdrenno.github.io/Estatistica/</t>
+  </si>
+  <si>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2026</t>
   </si>
 </sst>
 </file>
@@ -837,10 +834,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1131,21 +1124,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:T41"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="10"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="2" width="2.26953125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="7.453125" style="5" customWidth="1"/>
-    <col min="4" max="13" width="8.1796875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="2.1796875" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9.453125" style="5" customWidth="1"/>
-    <col min="16" max="17" width="2.453125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.1796875" style="5" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1796875" style="5"/>
+    <col min="1" max="2" width="2.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="5" customWidth="1"/>
+    <col min="4" max="13" width="8.140625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="2.140625" style="5" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" style="5" customWidth="1"/>
+    <col min="16" max="17" width="2.42578125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="5" hidden="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:20" ht="12" customHeight="1" thickBot="1">
       <c r="T1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="2:20" ht="10.5" customHeight="1">
@@ -1167,7 +1160,7 @@
       <c r="O2" s="7"/>
       <c r="P2" s="8"/>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="2:20" ht="10.5" customHeight="1">
@@ -1185,9 +1178,7 @@
       <c r="L3" s="60"/>
       <c r="M3" s="60"/>
       <c r="P3" s="10"/>
-      <c r="T3" t="s">
-        <v>46</v>
-      </c>
+      <c r="T3"/>
     </row>
     <row r="4" spans="2:20" ht="10.5" customHeight="1">
       <c r="B4" s="9"/>
@@ -1912,16 +1903,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:R41"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="10"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="2" width="2.26953125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="7.453125" style="5" customWidth="1"/>
-    <col min="4" max="13" width="8.1796875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="2.1796875" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9.453125" style="5" customWidth="1"/>
-    <col min="16" max="17" width="2.453125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.1796875" style="5" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1796875" style="5"/>
+    <col min="1" max="2" width="2.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="5" customWidth="1"/>
+    <col min="4" max="13" width="8.140625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="2.140625" style="5" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" style="5" customWidth="1"/>
+    <col min="16" max="17" width="2.42578125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="5" hidden="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="12" customHeight="1" thickBot="1"/>
@@ -2682,9 +2673,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
